--- a/TDD_examples/CASE_2_ENEA_HTS_CICC/environment_input.xlsx
+++ b/TDD_examples/CASE_2_ENEA_HTS_CICC/environment_input.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ENVIRONMENT" sheetId="2" r:id="R034a2825062f42d8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ENVIRONMENT" sheetId="2" r:id="R4ae98f88d65d42f2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -17,9 +17,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">string</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Type of medium that fill the environment (defaults to Air)</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Air</x:t>
@@ -406,25 +403,25 @@
       <x:c r="C2" s="16" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D2" s="20" t="s">
+      <x:c r="D2" s="20" t="str">
+        <x:v>Type of medium that fills the environment (defaults to Air).</x:v>
+      </x:c>
+      <x:c r="E2" s="17" t="s">
         <x:v>3</x:v>
-      </x:c>
-      <x:c r="E2" s="17" t="s">
-        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="14.5" hidden="0" customHeight="1">
       <x:c r="A3" s="15" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B3" s="16" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B3" s="16" t="s">
+      <x:c r="C3" s="16" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C3" s="16" t="s">
+      <x:c r="D3" s="20" t="s">
         <x:v>7</x:v>
-      </x:c>
-      <x:c r="D3" s="20" t="s">
-        <x:v>8</x:v>
       </x:c>
       <x:c r="E3" s="16">
         <x:v>300.14999999999998</x:v>
@@ -432,16 +429,16 @@
     </x:row>
     <x:row r="4" ht="14.5" hidden="0" customHeight="1">
       <x:c r="A4" s="15" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B4" s="16" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="B4" s="16" t="s">
+      <x:c r="C4" s="16" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D4" s="20" t="s">
         <x:v>10</x:v>
-      </x:c>
-      <x:c r="C4" s="16" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D4" s="20" t="s">
-        <x:v>11</x:v>
       </x:c>
       <x:c r="E4" s="18" t="n">
         <x:v>101325</x:v>
